--- a/TB_BOM_2026.xlsx
+++ b/TB_BOM_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1aefba67a2305a7d/Documents/GitHub/USC-ASME-TigerBurn-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{78D3C34A-D728-4CD8-A926-F00C645BAA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CFE1C11-C058-43B8-BA95-11CD14B7D2F7}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{78D3C34A-D728-4CD8-A926-F00C645BAA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E413AE0-39CE-4C8C-AF5A-64CAF30B7399}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5E11D219-2DD1-4F5F-BD59-159B1B8915B2}"/>
   </bookViews>
@@ -165,7 +165,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,12 +181,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -224,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -248,9 +242,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -679,7 +670,7 @@
         <v>20</v>
       </c>
       <c r="E2" s="8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F2" s="5"/>
       <c r="H2" s="6">
@@ -689,27 +680,26 @@
         <v>1</v>
       </c>
       <c r="J2" s="8">
-        <f>6+0.5+1+1+1</f>
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="K2" s="4">
         <f>4+1+2+1+1+1</f>
         <v>10</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="8">
         <v>12</v>
       </c>
       <c r="M2" s="4">
         <f>SUM(H2:L2)*2</f>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="O2" s="4">
         <f t="shared" ref="O2:O7" si="0">SUM(B2:E2)+M2</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P2" s="4">
         <f>SUM(O2+O2*0.1)</f>
-        <v>165</v>
+        <v>166.1</v>
       </c>
       <c r="R2" s="4">
         <f>SUM(O2:O7)</f>
@@ -732,7 +722,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F3" s="5"/>
       <c r="H3" s="6">
@@ -740,24 +730,23 @@
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="8">
-        <f>1+1+2+2</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K3" s="4"/>
-      <c r="L3" s="9">
+      <c r="L3" s="8">
         <v>1</v>
       </c>
       <c r="M3" s="4">
         <f t="shared" ref="M3:M7" si="1">SUM(H3:L3)*2</f>
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O3" s="4">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="P3" s="4">
         <f t="shared" ref="P3:P6" si="2">SUM(O3+O3*0.1)</f>
-        <v>64.900000000000006</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -774,7 +763,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5"/>
       <c r="H4" s="6">
@@ -785,7 +774,7 @@
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="9">
+      <c r="L4" s="8">
         <v>1</v>
       </c>
       <c r="M4" s="4">
@@ -794,11 +783,11 @@
       </c>
       <c r="O4" s="4">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="P4" s="4">
         <f t="shared" si="2"/>
-        <v>38.5</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -903,40 +892,40 @@
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="H10" s="2">
         <f>SUM(E2, (I2+J2+K2+L2)*2)</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J10" s="2">
         <f>P2-H2*2-D2-C2-B2</f>
-        <v>105</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="H11" s="2">
         <f>E3+((J3+L3)*2)</f>
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J11" s="2">
         <f>P3-H3*2-D3-C3</f>
-        <v>35.900000000000006</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="H12" s="2">
         <f>E4+I4*2</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="2">
         <f>P4-H4*2-D4-C4-B4</f>
-        <v>21.5</v>
+        <v>30.299999999999997</v>
       </c>
     </row>
   </sheetData>
